--- a/administrative_forms/007_power_line_safety_inspection_form--administrative_forms.xlsx
+++ b/administrative_forms/007_power_line_safety_inspection_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>inspection_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Inspection Findings</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Inspection Date</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Date of the inspection</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inspection Date</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Name of the employee conducting the inspection</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>inspection_location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Employee Name</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Inspection Location</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Location of the inspection</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>hazard_report</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Work Location</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Hazard Report</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Description of the hazards found during the inspection</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>action_plan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hazard Report</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Action Plan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Description of the action plan for each hazard</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inspection Findings</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Additional comments or notes from the inspector</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>hazards_found</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Action Plan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Hazards Found</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select the type of hazards found during the inspection</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>hazards_mitigated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Hazards Mitigated</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select the hazards that have been mitigated</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -699,228 +731,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Indicate the status of the form</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>first-page</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -937,10 +766,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -965,7 +794,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>inspection_location_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -982,7 +811,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>inspection_location_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -999,85 +828,153 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>inspection_location_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no_hazards</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No Hazards</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>hazards_found_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>minor_hazards</t>
+          <t>no_hazards</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minor Hazards</t>
+          <t>No Hazards</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>hazards_found_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>major_hazards</t>
+          <t>minor_hazards</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Major Hazards</t>
+          <t>Minor Hazards</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>hazards_found_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>major_hazards</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Not Required</t>
+          <t>Major Hazards</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>hazards_mitigated_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>line_crew</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Line Crew</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hazards_mitigated_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>transmission_station</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Transmission Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>status_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>status_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>status_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
